--- a/results/block3_results/cad-rads/Normal_2/patient_report_Normal_2.xlsx
+++ b/results/block3_results/cad-rads/Normal_2/patient_report_Normal_2.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>97.09260018453763</v>
+        <v>93.94116395779251</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
@@ -555,7 +555,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
         <v>17</v>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>77.18920566901018</v>
+        <v>71.52196268718048</v>
       </c>
       <c r="E2" t="n">
         <v>4</v>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>97.09260018453763</v>
+        <v>93.94116395779251</v>
       </c>
       <c r="E3" t="n">
         <v>4</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>77.07747077631713</v>
+        <v>78.10357840320319</v>
       </c>
       <c r="E4" t="n">
         <v>4</v>
@@ -793,16 +793,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>77.18920566901018</v>
+        <v>71.52196268718048</v>
       </c>
       <c r="C2" t="n">
-        <v>10.21499324701531</v>
+        <v>25.17429823390993</v>
       </c>
       <c r="D2" t="n">
         <v>259</v>
       </c>
       <c r="E2" t="n">
-        <v>184</v>
+        <v>120</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>77.18920566901018</v>
+        <v>71.52196268718048</v>
       </c>
     </row>
     <row r="3">
@@ -836,10 +836,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>73.34886027528022</v>
+        <v>59.6439378950183</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.5902910461319972</v>
       </c>
       <c r="D3" t="n">
         <v>698</v>
@@ -863,15 +863,15 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Severe stenosis</t>
+          <t>Moderate stenosis</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>73.34886027528022</v>
+        <v>59.6439378950183</v>
       </c>
     </row>
     <row r="4">
@@ -879,7 +879,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>62.35848794919296</v>
+        <v>53.97862554491246</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -888,7 +888,7 @@
         <v>577</v>
       </c>
       <c r="E4" t="n">
-        <v>502</v>
+        <v>439</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>62.35848794919296</v>
+        <v>53.97862554491246</v>
       </c>
     </row>
     <row r="5">
@@ -922,7 +922,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>49.71907711687957</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -931,7 +931,7 @@
         <v>499</v>
       </c>
       <c r="E5" t="n">
-        <v>352</v>
+        <v>121</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -949,15 +949,15 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Mild stenosis</t>
+          <t>No visible stenosis</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>49.71907711687957</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -965,7 +965,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>97.09260018453763</v>
+        <v>93.94116395779251</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>97.09260018453763</v>
+        <v>93.94116395779251</v>
       </c>
     </row>
     <row r="7">
@@ -1008,7 +1008,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>53.99143325328575</v>
+        <v>57.78675001947619</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -1017,7 +1017,7 @@
         <v>358</v>
       </c>
       <c r="E7" t="n">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>53.99143325328575</v>
+        <v>57.78675001947619</v>
       </c>
     </row>
     <row r="8">
@@ -1051,7 +1051,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>55.46926195631712</v>
+        <v>67.81264134577366</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -1060,7 +1060,7 @@
         <v>577</v>
       </c>
       <c r="E8" t="n">
-        <v>547</v>
+        <v>518</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>55.46926195631712</v>
+        <v>67.81264134577366</v>
       </c>
     </row>
     <row r="9">
@@ -1094,16 +1094,16 @@
         <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>67.32217751427825</v>
+        <v>45.89948455234406</v>
       </c>
       <c r="C9" t="n">
-        <v>6.578003633340263</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>83</v>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1121,15 +1121,15 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Moderate stenosis</t>
+          <t>Mild stenosis</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>67.32217751427825</v>
+        <v>45.89948455234406</v>
       </c>
     </row>
     <row r="10">
@@ -1137,7 +1137,7 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>77.07747077631713</v>
+        <v>78.10357840320319</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>77.07747077631713</v>
+        <v>78.10357840320319</v>
       </c>
     </row>
     <row r="11">
@@ -1180,7 +1180,7 @@
         <v>13</v>
       </c>
       <c r="B11" t="n">
-        <v>64.47148623624821</v>
+        <v>62.21685031125167</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -1189,7 +1189,7 @@
         <v>614</v>
       </c>
       <c r="E11" t="n">
-        <v>579</v>
+        <v>519</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>64.47148623624821</v>
+        <v>62.21685031125167</v>
       </c>
     </row>
     <row r="12">
@@ -1223,7 +1223,7 @@
         <v>17</v>
       </c>
       <c r="B12" t="n">
-        <v>76.76616129235144</v>
+        <v>77.96856518034964</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -1232,7 +1232,7 @@
         <v>792</v>
       </c>
       <c r="E12" t="n">
-        <v>763</v>
+        <v>728</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>76.76616129235144</v>
+        <v>77.96856518034964</v>
       </c>
     </row>
     <row r="13">
@@ -1266,16 +1266,16 @@
         <v>19</v>
       </c>
       <c r="B13" t="n">
-        <v>93.22655280984159</v>
+        <v>90.14057811460118</v>
       </c>
       <c r="C13" t="n">
-        <v>13.29707882025487</v>
+        <v>7.760426152324122</v>
       </c>
       <c r="D13" t="n">
         <v>471</v>
       </c>
       <c r="E13" t="n">
-        <v>327</v>
+        <v>195</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>93.22655280984159</v>
+        <v>90.14057811460118</v>
       </c>
     </row>
   </sheetData>
@@ -1380,16 +1380,16 @@
         <v>19</v>
       </c>
       <c r="B2" t="n">
-        <v>93.22655280984159</v>
+        <v>90.14057811460118</v>
       </c>
       <c r="C2" t="n">
-        <v>13.29707882025487</v>
+        <v>7.760426152324122</v>
       </c>
       <c r="D2" t="n">
         <v>471</v>
       </c>
       <c r="E2" t="n">
-        <v>327</v>
+        <v>195</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>93.22655280984159</v>
+        <v>90.14057811460118</v>
       </c>
     </row>
   </sheetData>
